--- a/validation/reference_models/GenericSolar_ReferenceModel.xlsx
+++ b/validation/reference_models/GenericSolar_ReferenceModel.xlsx
@@ -9367,6 +9367,179 @@
         <v>24750.0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Schedule rescale factor (gearing-cap senior debt / DSCR-sized debt, capped at 1)</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>IF(C14&gt;0,MIN(1,C16/C14),1)</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rescaled debt service capacity (capacity x rescale factor)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f>E13*$C$17</f>
+      </c>
+      <c r="F18">
+        <f>F13*$C$17</f>
+      </c>
+      <c r="G18">
+        <f>G13*$C$17</f>
+      </c>
+      <c r="H18">
+        <f>H13*$C$17</f>
+      </c>
+      <c r="I18">
+        <f>I13*$C$17</f>
+      </c>
+      <c r="J18">
+        <f>J13*$C$17</f>
+      </c>
+      <c r="K18">
+        <f>K13*$C$17</f>
+      </c>
+      <c r="L18">
+        <f>L13*$C$17</f>
+      </c>
+      <c r="M18">
+        <f>M13*$C$17</f>
+      </c>
+      <c r="N18">
+        <f>N13*$C$17</f>
+      </c>
+      <c r="O18">
+        <f>O13*$C$17</f>
+      </c>
+      <c r="P18">
+        <f>P13*$C$17</f>
+      </c>
+      <c r="Q18">
+        <f>Q13*$C$17</f>
+      </c>
+      <c r="R18">
+        <f>R13*$C$17</f>
+      </c>
+      <c r="S18">
+        <f>S13*$C$17</f>
+      </c>
+      <c r="T18">
+        <f>T13*$C$17</f>
+      </c>
+      <c r="U18">
+        <f>U13*$C$17</f>
+      </c>
+      <c r="V18">
+        <f>V13*$C$17</f>
+      </c>
+      <c r="W18">
+        <f>W13*$C$17</f>
+      </c>
+      <c r="X18">
+        <f>X13*$C$17</f>
+      </c>
+      <c r="Y18">
+        <f>Y13*$C$17</f>
+      </c>
+      <c r="Z18">
+        <f>Z13*$C$17</f>
+      </c>
+      <c r="AA18">
+        <f>AA13*$C$17</f>
+      </c>
+      <c r="AB18">
+        <f>AB13*$C$17</f>
+      </c>
+      <c r="AC18">
+        <f>AC13*$C$17</f>
+      </c>
+      <c r="AD18">
+        <f>AD13*$C$17</f>
+      </c>
+      <c r="AE18">
+        <f>AE13*$C$17</f>
+      </c>
+      <c r="AF18">
+        <f>AF13*$C$17</f>
+      </c>
+      <c r="AG18">
+        <f>AG13*$C$17</f>
+      </c>
+      <c r="AH18">
+        <f>AH13*$C$17</f>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -9773,120 +9946,91 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <f>MIN(E13,E20+E21)</f>
-        <v>1316.53515625</v>
+        <f>MIN(E18,E20+E21)</f>
       </c>
       <c r="F22">
-        <f>MIN(F13,F20+F21)</f>
-        <v>1316.53515625</v>
+        <f>MIN(F18,F20+F21)</f>
       </c>
       <c r="G22">
-        <f>MIN(G13,G20+G21)</f>
-        <v>1334.2736459375003</v>
+        <f>MIN(G18,G20+G21)</f>
       </c>
       <c r="H22">
-        <f>MIN(H13,H20+H21)</f>
-        <v>1334.2736459375003</v>
+        <f>MIN(H18,H20+H21)</f>
       </c>
       <c r="I22">
-        <f>MIN(I13,I20+I21)</f>
-        <v>1352.2848423808255</v>
+        <f>MIN(I18,I20+I21)</f>
       </c>
       <c r="J22">
-        <f>MIN(J13,J20+J21)</f>
-        <v>1352.2848423808255</v>
+        <f>MIN(J18,J20+J21)</f>
       </c>
       <c r="K22">
-        <f>MIN(K13,K20+K21)</f>
-        <v>1370.572893271528</v>
+        <f>MIN(K18,K20+K21)</f>
       </c>
       <c r="L22">
-        <f>MIN(L13,L20+L21)</f>
-        <v>1370.572893271528</v>
+        <f>MIN(L18,L20+L21)</f>
       </c>
       <c r="M22">
-        <f>MIN(M13,M20+M21)</f>
-        <v>1389.1420084564104</v>
+        <f>MIN(M18,M20+M21)</f>
       </c>
       <c r="N22">
-        <f>MIN(N13,N20+N21)</f>
-        <v>1389.1420084564104</v>
+        <f>MIN(N18,N20+N21)</f>
       </c>
       <c r="O22">
-        <f>MIN(O13,O20+O21)</f>
-        <v>1407.9964608495163</v>
+        <f>MIN(O18,O20+O21)</f>
       </c>
       <c r="P22">
-        <f>MIN(P13,P20+P21)</f>
-        <v>1407.9964608495163</v>
+        <f>MIN(P18,P20+P21)</f>
       </c>
       <c r="Q22">
-        <f>MIN(Q13,Q20+Q21)</f>
-        <v>1427.140587357091</v>
+        <f>MIN(Q18,Q20+Q21)</f>
       </c>
       <c r="R22">
-        <f>MIN(R13,R20+R21)</f>
-        <v>1427.140587357091</v>
+        <f>MIN(R18,R20+R21)</f>
       </c>
       <c r="S22">
-        <f>MIN(S13,S20+S21)</f>
-        <v>1446.578789815682</v>
+        <f>MIN(S18,S20+S21)</f>
       </c>
       <c r="T22">
-        <f>MIN(T13,T20+T21)</f>
-        <v>1446.578789815682</v>
+        <f>MIN(T18,T20+T21)</f>
       </c>
       <c r="U22">
-        <f>MIN(U13,U20+U21)</f>
-        <v>1466.3155359435718</v>
+        <f>MIN(U18,U20+U21)</f>
       </c>
       <c r="V22">
-        <f>MIN(V13,V20+V21)</f>
-        <v>1466.3155359435718</v>
+        <f>MIN(V18,V20+V21)</f>
       </c>
       <c r="W22">
-        <f>MIN(W13,W20+W21)</f>
-        <v>1486.3553603056978</v>
+        <f>MIN(W18,W20+W21)</f>
       </c>
       <c r="X22">
-        <f>MIN(X13,X20+X21)</f>
-        <v>1486.3553603056978</v>
+        <f>MIN(X18,X20+X21)</f>
       </c>
       <c r="Y22">
-        <f>MIN(Y13,Y20+Y21)</f>
-        <v>1635.9356445804406</v>
+        <f>MIN(Y18,Y20+Y21)</f>
       </c>
       <c r="Z22">
-        <f>MIN(Z13,Z20+Z21)</f>
-        <v>1635.9356445804406</v>
+        <f>MIN(Z18,Z20+Z21)</f>
       </c>
       <c r="AA22">
-        <f>MIN(AA13,AA20+AA21)</f>
-        <v>1658.6528872456738</v>
+        <f>MIN(AA18,AA20+AA21)</f>
       </c>
       <c r="AB22">
-        <f>MIN(AB13,AB20+AB21)</f>
-        <v>1628.167382316978</v>
+        <f>MIN(AB18,AB20+AB21)</f>
       </c>
       <c r="AC22">
-        <f>MIN(AC13,AC20+AC21)</f>
-        <v>0.0</v>
+        <f>MIN(AC18,AC20+AC21)</f>
       </c>
       <c r="AD22">
-        <f>MIN(AD13,AD20+AD21)</f>
-        <v>0.0</v>
+        <f>MIN(AD18,AD20+AD21)</f>
       </c>
       <c r="AE22">
-        <f>MIN(AE13,AE20+AE21)</f>
-        <v>0.0</v>
+        <f>MIN(AE18,AE20+AE21)</f>
       </c>
       <c r="AF22">
-        <f>MIN(AF13,AF20+AF21)</f>
-        <v>0.0</v>
+        <f>MIN(AF18,AF20+AF21)</f>
       </c>
       <c r="AG22">
-        <f>MIN(AG13,AG20+AG21)</f>
-        <v>0.0</v>
+        <f>MIN(AG18,AG20+AG21)</f>
       </c>
       <c r="AH22">
         <f>AH23+AH21</f>
